--- a/outputs/metformin_structured_extracted.xlsx
+++ b/outputs/metformin_structured_extracted.xlsx
@@ -7,14 +7,15 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Studies" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arms" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eligibility" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outcomes" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation_Log" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flattened_View" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables_Matrix" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Master_Extraction_Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Studies" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arms" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eligibility" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outcomes" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provenance" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation_Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flattened_View" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables_Matrix" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,13 +39,53 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F1F1F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001B365D"/>
+        <bgColor rgb="001B365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5597"/>
+        <bgColor rgb="002F5597"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+        <bgColor rgb="00F8FAFC"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -79,9 +120,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -450,6 +513,2344 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AX15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="27" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="16" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="38" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
+    <col width="10" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="10" customWidth="1" min="30" max="30"/>
+    <col width="28" customWidth="1" min="31" max="31"/>
+    <col width="10" customWidth="1" min="32" max="32"/>
+    <col width="12" customWidth="1" min="33" max="33"/>
+    <col width="10" customWidth="1" min="34" max="34"/>
+    <col width="32" customWidth="1" min="35" max="35"/>
+    <col width="10" customWidth="1" min="36" max="36"/>
+    <col width="10" customWidth="1" min="37" max="37"/>
+    <col width="10" customWidth="1" min="38" max="38"/>
+    <col width="32" customWidth="1" min="39" max="39"/>
+    <col width="10" customWidth="1" min="40" max="40"/>
+    <col width="10" customWidth="1" min="41" max="41"/>
+    <col width="10" customWidth="1" min="42" max="42"/>
+    <col width="24" customWidth="1" min="43" max="43"/>
+    <col width="10" customWidth="1" min="44" max="44"/>
+    <col width="10" customWidth="1" min="45" max="45"/>
+    <col width="10" customWidth="1" min="46" max="46"/>
+    <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="10" customWidth="1" min="48" max="48"/>
+    <col width="10" customWidth="1" min="49" max="49"/>
+    <col width="10" customWidth="1" min="50" max="50"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>STUDY &amp; INTERVENTION ARMS</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ELIGIBILITY CRITERIA</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
+      <c r="T1" s="1" t="n"/>
+      <c r="U1" s="1" t="n"/>
+      <c r="V1" s="1" t="n"/>
+      <c r="W1" s="1" t="n"/>
+      <c r="X1" s="1" t="n"/>
+      <c r="Y1" s="1" t="n"/>
+      <c r="Z1" s="1" t="n"/>
+      <c r="AA1" s="1" t="n"/>
+      <c r="AB1" s="1" t="n"/>
+      <c r="AC1" s="1" t="n"/>
+      <c r="AD1" s="1" t="n"/>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>POPULATION STRATIFICATION</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="n"/>
+      <c r="AG1" s="1" t="n"/>
+      <c r="AH1" s="1" t="n"/>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>CLINICAL VARIABLES &amp; OUTCOMES</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="n"/>
+      <c r="AK1" s="1" t="n"/>
+      <c r="AL1" s="1" t="n"/>
+      <c r="AM1" s="1" t="n"/>
+      <c r="AN1" s="1" t="n"/>
+      <c r="AO1" s="1" t="n"/>
+      <c r="AP1" s="1" t="n"/>
+      <c r="AQ1" s="1" t="n"/>
+      <c r="AR1" s="1" t="n"/>
+      <c r="AS1" s="1" t="n"/>
+      <c r="AT1" s="1" t="n"/>
+      <c r="AU1" s="1" t="n"/>
+      <c r="AV1" s="1" t="n"/>
+      <c r="AW1" s="1" t="n"/>
+      <c r="AX1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Study ID</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Group / Arm Name</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Intervention Type</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Dose</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Frequency</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Study Phase</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Period of Study</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Total Cohort (N)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Arm Sample Size (N)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Age</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Bmi</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="n"/>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n"/>
+      <c r="T2" s="2" t="n"/>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>Baseline Fasting Glucose</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="n"/>
+      <c r="W2" s="2" t="n"/>
+      <c r="X2" s="2" t="n"/>
+      <c r="Y2" s="2" t="n"/>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>Baseline Impaired Glucose Tolerance</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="n"/>
+      <c r="AB2" s="2" t="n"/>
+      <c r="AC2" s="2" t="n"/>
+      <c r="AD2" s="2" t="n"/>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>Race / Ethnicity</t>
+        </is>
+      </c>
+      <c r="AF2" s="2" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>Timepoint</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="n"/>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>Weight Loss</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="n"/>
+      <c r="AK2" s="2" t="n"/>
+      <c r="AL2" s="2" t="n"/>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>Waist Circumference Reduction</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="n"/>
+      <c r="AO2" s="2" t="n"/>
+      <c r="AP2" s="2" t="n"/>
+      <c r="AQ2" s="2" t="inlineStr">
+        <is>
+          <t>Weight Loss &gt;= 5%</t>
+        </is>
+      </c>
+      <c r="AR2" s="2" t="n"/>
+      <c r="AS2" s="2" t="n"/>
+      <c r="AT2" s="2" t="n"/>
+      <c r="AU2" s="2" t="inlineStr">
+        <is>
+          <t>High Adherence</t>
+        </is>
+      </c>
+      <c r="AV2" s="2" t="n"/>
+      <c r="AW2" s="2" t="n"/>
+      <c r="AX2" s="2" t="n"/>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="3" t="inlineStr"/>
+      <c r="B3" s="3" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr"/>
+      <c r="D3" s="3" t="inlineStr"/>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" s="3" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Number</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Value / Range</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>Value / Range</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>Value / Range</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>&lt;</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>Value / Range</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AF3" s="3" t="inlineStr"/>
+      <c r="AG3" s="4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="inlineStr">
+        <is>
+          <t>Value / Mean / Events</t>
+        </is>
+      </c>
+      <c r="AJ3" s="4" t="inlineStr">
+        <is>
+          <t>SD / %</t>
+        </is>
+      </c>
+      <c r="AK3" s="4" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="AL3" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="AM3" s="4" t="inlineStr">
+        <is>
+          <t>Value / Mean / Events</t>
+        </is>
+      </c>
+      <c r="AN3" s="4" t="inlineStr">
+        <is>
+          <t>SD / %</t>
+        </is>
+      </c>
+      <c r="AO3" s="4" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="AP3" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="AQ3" s="4" t="inlineStr">
+        <is>
+          <t>Value / Mean / Events</t>
+        </is>
+      </c>
+      <c r="AR3" s="4" t="inlineStr">
+        <is>
+          <t>SD / %</t>
+        </is>
+      </c>
+      <c r="AS3" s="4" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="AT3" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="AU3" s="4" t="inlineStr">
+        <is>
+          <t>Value / Mean / Events</t>
+        </is>
+      </c>
+      <c r="AV3" s="4" t="inlineStr">
+        <is>
+          <t>SD / %</t>
+        </is>
+      </c>
+      <c r="AW3" s="4" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="AX3" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Metformin 850mg</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>experimental</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>850.0 mg</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>2.0 twice daily</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>790</v>
+      </c>
+      <c r="K4" s="6" t="n"/>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="O4" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S4" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="T4" s="6" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="U4" s="6" t="n"/>
+      <c r="V4" s="6" t="n"/>
+      <c r="W4" s="6" t="n"/>
+      <c r="X4" s="6" t="inlineStr">
+        <is>
+          <t>95.0 – 125.0</t>
+        </is>
+      </c>
+      <c r="Y4" s="6" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Z4" s="6" t="n"/>
+      <c r="AA4" s="6" t="n"/>
+      <c r="AB4" s="6" t="n"/>
+      <c r="AC4" s="6" t="inlineStr">
+        <is>
+          <t>140.0 – 199.0</t>
+        </is>
+      </c>
+      <c r="AD4" s="6" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="AE4" s="6" t="inlineStr">
+        <is>
+          <t>African American</t>
+        </is>
+      </c>
+      <c r="AF4" s="6" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AG4" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH4" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="AI4" s="6" t="n"/>
+      <c r="AJ4" s="6" t="n"/>
+      <c r="AK4" s="6" t="n"/>
+      <c r="AL4" s="6" t="n"/>
+      <c r="AM4" s="6" t="n"/>
+      <c r="AN4" s="6" t="n"/>
+      <c r="AO4" s="6" t="n"/>
+      <c r="AP4" s="6" t="n"/>
+      <c r="AQ4" s="6" t="n"/>
+      <c r="AR4" s="6" t="n"/>
+      <c r="AS4" s="6" t="n"/>
+      <c r="AT4" s="6" t="n"/>
+      <c r="AU4" s="6" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="AV4" s="6" t="n"/>
+      <c r="AW4" s="6" t="n"/>
+      <c r="AX4" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Metformin 850mg</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>experimental</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>850.0 mg</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>2.0 twice daily</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J5" s="8" t="n">
+        <v>790</v>
+      </c>
+      <c r="K5" s="8" t="n"/>
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N5" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="P5" s="8" t="n"/>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="n"/>
+      <c r="V5" s="8" t="n"/>
+      <c r="W5" s="8" t="n"/>
+      <c r="X5" s="8" t="inlineStr">
+        <is>
+          <t>95.0 – 125.0</t>
+        </is>
+      </c>
+      <c r="Y5" s="8" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Z5" s="8" t="n"/>
+      <c r="AA5" s="8" t="n"/>
+      <c r="AB5" s="8" t="n"/>
+      <c r="AC5" s="8" t="inlineStr">
+        <is>
+          <t>140.0 – 199.0</t>
+        </is>
+      </c>
+      <c r="AD5" s="8" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="AE5" s="8" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="AF5" s="8" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AG5" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH5" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="AI5" s="8" t="n"/>
+      <c r="AJ5" s="8" t="n"/>
+      <c r="AK5" s="8" t="n"/>
+      <c r="AL5" s="8" t="n"/>
+      <c r="AM5" s="8" t="n"/>
+      <c r="AN5" s="8" t="n"/>
+      <c r="AO5" s="8" t="n"/>
+      <c r="AP5" s="8" t="n"/>
+      <c r="AQ5" s="8" t="n"/>
+      <c r="AR5" s="8" t="n"/>
+      <c r="AS5" s="8" t="n"/>
+      <c r="AT5" s="8" t="n"/>
+      <c r="AU5" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV5" s="8" t="n"/>
+      <c r="AW5" s="8" t="n"/>
+      <c r="AX5" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Metformin 850mg</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>experimental</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>850.0 mg</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>2.0 twice daily</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>790</v>
+      </c>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="T6" s="6" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
+      <c r="W6" s="6" t="n"/>
+      <c r="X6" s="6" t="inlineStr">
+        <is>
+          <t>95.0 – 125.0</t>
+        </is>
+      </c>
+      <c r="Y6" s="6" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Z6" s="6" t="n"/>
+      <c r="AA6" s="6" t="n"/>
+      <c r="AB6" s="6" t="n"/>
+      <c r="AC6" s="6" t="inlineStr">
+        <is>
+          <t>140.0 – 199.0</t>
+        </is>
+      </c>
+      <c r="AD6" s="6" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="AE6" s="6" t="inlineStr">
+        <is>
+          <t>Caucasian</t>
+        </is>
+      </c>
+      <c r="AF6" s="6" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AG6" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH6" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="AI6" s="6" t="n"/>
+      <c r="AJ6" s="6" t="n"/>
+      <c r="AK6" s="6" t="n"/>
+      <c r="AL6" s="6" t="n"/>
+      <c r="AM6" s="6" t="n"/>
+      <c r="AN6" s="6" t="n"/>
+      <c r="AO6" s="6" t="n"/>
+      <c r="AP6" s="6" t="n"/>
+      <c r="AQ6" s="6" t="n"/>
+      <c r="AR6" s="6" t="n"/>
+      <c r="AS6" s="6" t="n"/>
+      <c r="AT6" s="6" t="n"/>
+      <c r="AU6" s="6" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="AV6" s="6" t="n"/>
+      <c r="AW6" s="6" t="n"/>
+      <c r="AX6" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Metformin 850mg</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>experimental</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>850.0 mg</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>2.0 twice daily</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J7" s="8" t="n">
+        <v>790</v>
+      </c>
+      <c r="K7" s="8" t="n"/>
+      <c r="L7" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="n"/>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="n"/>
+      <c r="V7" s="8" t="n"/>
+      <c r="W7" s="8" t="n"/>
+      <c r="X7" s="8" t="inlineStr">
+        <is>
+          <t>95.0 – 125.0</t>
+        </is>
+      </c>
+      <c r="Y7" s="8" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Z7" s="8" t="n"/>
+      <c r="AA7" s="8" t="n"/>
+      <c r="AB7" s="8" t="n"/>
+      <c r="AC7" s="8" t="inlineStr">
+        <is>
+          <t>140.0 – 199.0</t>
+        </is>
+      </c>
+      <c r="AD7" s="8" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="AE7" s="8" t="inlineStr">
+        <is>
+          <t>Hispanic</t>
+        </is>
+      </c>
+      <c r="AF7" s="8" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AG7" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH7" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="AI7" s="8" t="n"/>
+      <c r="AJ7" s="8" t="n"/>
+      <c r="AK7" s="8" t="n"/>
+      <c r="AL7" s="8" t="n"/>
+      <c r="AM7" s="8" t="n"/>
+      <c r="AN7" s="8" t="n"/>
+      <c r="AO7" s="8" t="n"/>
+      <c r="AP7" s="8" t="n"/>
+      <c r="AQ7" s="8" t="n"/>
+      <c r="AR7" s="8" t="n"/>
+      <c r="AS7" s="8" t="n"/>
+      <c r="AT7" s="8" t="n"/>
+      <c r="AU7" s="8" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="AV7" s="8" t="n"/>
+      <c r="AW7" s="8" t="n"/>
+      <c r="AX7" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Metformin 850mg</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>experimental</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>850.0 mg</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>2.0 twice daily</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>790</v>
+      </c>
+      <c r="K8" s="6" t="n"/>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="O8" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="P8" s="6" t="n"/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="T8" s="6" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="U8" s="6" t="n"/>
+      <c r="V8" s="6" t="n"/>
+      <c r="W8" s="6" t="n"/>
+      <c r="X8" s="6" t="inlineStr">
+        <is>
+          <t>95.0 – 125.0</t>
+        </is>
+      </c>
+      <c r="Y8" s="6" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Z8" s="6" t="n"/>
+      <c r="AA8" s="6" t="n"/>
+      <c r="AB8" s="6" t="n"/>
+      <c r="AC8" s="6" t="inlineStr">
+        <is>
+          <t>140.0 – 199.0</t>
+        </is>
+      </c>
+      <c r="AD8" s="6" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="AE8" s="6" t="inlineStr">
+        <is>
+          <t>Native American</t>
+        </is>
+      </c>
+      <c r="AF8" s="6" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AG8" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH8" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="AI8" s="6" t="n"/>
+      <c r="AJ8" s="6" t="n"/>
+      <c r="AK8" s="6" t="n"/>
+      <c r="AL8" s="6" t="n"/>
+      <c r="AM8" s="6" t="n"/>
+      <c r="AN8" s="6" t="n"/>
+      <c r="AO8" s="6" t="n"/>
+      <c r="AP8" s="6" t="n"/>
+      <c r="AQ8" s="6" t="n"/>
+      <c r="AR8" s="6" t="n"/>
+      <c r="AS8" s="6" t="n"/>
+      <c r="AT8" s="6" t="n"/>
+      <c r="AU8" s="6" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="AV8" s="6" t="n"/>
+      <c r="AW8" s="6" t="n"/>
+      <c r="AX8" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Metformin 850mg</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>experimental</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>850.0 mg</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>2.0 twice daily</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>790</v>
+      </c>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="P9" s="8" t="n"/>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R9" s="8" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S9" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="n"/>
+      <c r="V9" s="8" t="n"/>
+      <c r="W9" s="8" t="n"/>
+      <c r="X9" s="8" t="inlineStr">
+        <is>
+          <t>95.0 – 125.0</t>
+        </is>
+      </c>
+      <c r="Y9" s="8" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Z9" s="8" t="n"/>
+      <c r="AA9" s="8" t="n"/>
+      <c r="AB9" s="8" t="n"/>
+      <c r="AC9" s="8" t="inlineStr">
+        <is>
+          <t>140.0 – 199.0</t>
+        </is>
+      </c>
+      <c r="AD9" s="8" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="AE9" s="8" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AF9" s="8" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AG9" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH9" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="AI9" s="8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ9" s="8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AK9" s="8" t="n"/>
+      <c r="AL9" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AM9" s="8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AN9" s="8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AO9" s="8" t="n"/>
+      <c r="AP9" s="8" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="AQ9" s="8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR9" s="8" t="n"/>
+      <c r="AS9" s="8" t="n"/>
+      <c r="AT9" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AU9" s="8" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="AV9" s="8" t="n"/>
+      <c r="AW9" s="8" t="n"/>
+      <c r="AX9" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>2.0 twice daily</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>783</v>
+      </c>
+      <c r="K10" s="6" t="n"/>
+      <c r="L10" s="6" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="O10" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="P10" s="6" t="n"/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S10" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="T10" s="6" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="U10" s="6" t="n"/>
+      <c r="V10" s="6" t="n"/>
+      <c r="W10" s="6" t="n"/>
+      <c r="X10" s="6" t="inlineStr">
+        <is>
+          <t>95.0 – 125.0</t>
+        </is>
+      </c>
+      <c r="Y10" s="6" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Z10" s="6" t="n"/>
+      <c r="AA10" s="6" t="n"/>
+      <c r="AB10" s="6" t="n"/>
+      <c r="AC10" s="6" t="inlineStr">
+        <is>
+          <t>140.0 – 199.0</t>
+        </is>
+      </c>
+      <c r="AD10" s="6" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="AE10" s="6" t="inlineStr">
+        <is>
+          <t>African American</t>
+        </is>
+      </c>
+      <c r="AF10" s="6" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AG10" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH10" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="AI10" s="6" t="n"/>
+      <c r="AJ10" s="6" t="n"/>
+      <c r="AK10" s="6" t="n"/>
+      <c r="AL10" s="6" t="n"/>
+      <c r="AM10" s="6" t="n"/>
+      <c r="AN10" s="6" t="n"/>
+      <c r="AO10" s="6" t="n"/>
+      <c r="AP10" s="6" t="n"/>
+      <c r="AQ10" s="6" t="n"/>
+      <c r="AR10" s="6" t="n"/>
+      <c r="AS10" s="6" t="n"/>
+      <c r="AT10" s="6" t="n"/>
+      <c r="AU10" s="6" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV10" s="6" t="n"/>
+      <c r="AW10" s="6" t="n"/>
+      <c r="AX10" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>2.0 twice daily</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J11" s="8" t="n">
+        <v>783</v>
+      </c>
+      <c r="K11" s="8" t="n"/>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="P11" s="8" t="n"/>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R11" s="8" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="n"/>
+      <c r="V11" s="8" t="n"/>
+      <c r="W11" s="8" t="n"/>
+      <c r="X11" s="8" t="inlineStr">
+        <is>
+          <t>95.0 – 125.0</t>
+        </is>
+      </c>
+      <c r="Y11" s="8" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Z11" s="8" t="n"/>
+      <c r="AA11" s="8" t="n"/>
+      <c r="AB11" s="8" t="n"/>
+      <c r="AC11" s="8" t="inlineStr">
+        <is>
+          <t>140.0 – 199.0</t>
+        </is>
+      </c>
+      <c r="AD11" s="8" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="AE11" s="8" t="inlineStr">
+        <is>
+          <t>Asian</t>
+        </is>
+      </c>
+      <c r="AF11" s="8" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AG11" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH11" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="AI11" s="8" t="n"/>
+      <c r="AJ11" s="8" t="n"/>
+      <c r="AK11" s="8" t="n"/>
+      <c r="AL11" s="8" t="n"/>
+      <c r="AM11" s="8" t="n"/>
+      <c r="AN11" s="8" t="n"/>
+      <c r="AO11" s="8" t="n"/>
+      <c r="AP11" s="8" t="n"/>
+      <c r="AQ11" s="8" t="n"/>
+      <c r="AR11" s="8" t="n"/>
+      <c r="AS11" s="8" t="n"/>
+      <c r="AT11" s="8" t="n"/>
+      <c r="AU11" s="8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV11" s="8" t="n"/>
+      <c r="AW11" s="8" t="n"/>
+      <c r="AX11" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>2.0 twice daily</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>783</v>
+      </c>
+      <c r="K12" s="6" t="n"/>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="T12" s="6" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="U12" s="6" t="n"/>
+      <c r="V12" s="6" t="n"/>
+      <c r="W12" s="6" t="n"/>
+      <c r="X12" s="6" t="inlineStr">
+        <is>
+          <t>95.0 – 125.0</t>
+        </is>
+      </c>
+      <c r="Y12" s="6" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Z12" s="6" t="n"/>
+      <c r="AA12" s="6" t="n"/>
+      <c r="AB12" s="6" t="n"/>
+      <c r="AC12" s="6" t="inlineStr">
+        <is>
+          <t>140.0 – 199.0</t>
+        </is>
+      </c>
+      <c r="AD12" s="6" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="AE12" s="6" t="inlineStr">
+        <is>
+          <t>Caucasian</t>
+        </is>
+      </c>
+      <c r="AF12" s="6" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AG12" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="AI12" s="6" t="n"/>
+      <c r="AJ12" s="6" t="n"/>
+      <c r="AK12" s="6" t="n"/>
+      <c r="AL12" s="6" t="n"/>
+      <c r="AM12" s="6" t="n"/>
+      <c r="AN12" s="6" t="n"/>
+      <c r="AO12" s="6" t="n"/>
+      <c r="AP12" s="6" t="n"/>
+      <c r="AQ12" s="6" t="n"/>
+      <c r="AR12" s="6" t="n"/>
+      <c r="AS12" s="6" t="n"/>
+      <c r="AT12" s="6" t="n"/>
+      <c r="AU12" s="6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV12" s="6" t="n"/>
+      <c r="AW12" s="6" t="n"/>
+      <c r="AX12" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr"/>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>2.0 twice daily</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J13" s="8" t="n">
+        <v>783</v>
+      </c>
+      <c r="K13" s="8" t="n"/>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M13" s="8" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="O13" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="P13" s="8" t="n"/>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R13" s="8" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="n"/>
+      <c r="V13" s="8" t="n"/>
+      <c r="W13" s="8" t="n"/>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t>95.0 – 125.0</t>
+        </is>
+      </c>
+      <c r="Y13" s="8" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Z13" s="8" t="n"/>
+      <c r="AA13" s="8" t="n"/>
+      <c r="AB13" s="8" t="n"/>
+      <c r="AC13" s="8" t="inlineStr">
+        <is>
+          <t>140.0 – 199.0</t>
+        </is>
+      </c>
+      <c r="AD13" s="8" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="AE13" s="8" t="inlineStr">
+        <is>
+          <t>Hispanic</t>
+        </is>
+      </c>
+      <c r="AF13" s="8" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AG13" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH13" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="AI13" s="8" t="n"/>
+      <c r="AJ13" s="8" t="n"/>
+      <c r="AK13" s="8" t="n"/>
+      <c r="AL13" s="8" t="n"/>
+      <c r="AM13" s="8" t="n"/>
+      <c r="AN13" s="8" t="n"/>
+      <c r="AO13" s="8" t="n"/>
+      <c r="AP13" s="8" t="n"/>
+      <c r="AQ13" s="8" t="n"/>
+      <c r="AR13" s="8" t="n"/>
+      <c r="AS13" s="8" t="n"/>
+      <c r="AT13" s="8" t="n"/>
+      <c r="AU13" s="8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AV13" s="8" t="n"/>
+      <c r="AW13" s="8" t="n"/>
+      <c r="AX13" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>2.0 twice daily</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>783</v>
+      </c>
+      <c r="K14" s="6" t="n"/>
+      <c r="L14" s="6" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="O14" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="P14" s="6" t="n"/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="T14" s="6" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="U14" s="6" t="n"/>
+      <c r="V14" s="6" t="n"/>
+      <c r="W14" s="6" t="n"/>
+      <c r="X14" s="6" t="inlineStr">
+        <is>
+          <t>95.0 – 125.0</t>
+        </is>
+      </c>
+      <c r="Y14" s="6" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Z14" s="6" t="n"/>
+      <c r="AA14" s="6" t="n"/>
+      <c r="AB14" s="6" t="n"/>
+      <c r="AC14" s="6" t="inlineStr">
+        <is>
+          <t>140.0 – 199.0</t>
+        </is>
+      </c>
+      <c r="AD14" s="6" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="AE14" s="6" t="inlineStr">
+        <is>
+          <t>Native American</t>
+        </is>
+      </c>
+      <c r="AF14" s="6" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AG14" s="6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH14" s="6" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="AI14" s="6" t="n"/>
+      <c r="AJ14" s="6" t="n"/>
+      <c r="AK14" s="6" t="n"/>
+      <c r="AL14" s="6" t="n"/>
+      <c r="AM14" s="6" t="n"/>
+      <c r="AN14" s="6" t="n"/>
+      <c r="AO14" s="6" t="n"/>
+      <c r="AP14" s="6" t="n"/>
+      <c r="AQ14" s="6" t="n"/>
+      <c r="AR14" s="6" t="n"/>
+      <c r="AS14" s="6" t="n"/>
+      <c r="AT14" s="6" t="n"/>
+      <c r="AU14" s="6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AV14" s="6" t="n"/>
+      <c r="AW14" s="6" t="n"/>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>2.0 twice daily</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="I15" s="8" t="n">
+        <v>2155</v>
+      </c>
+      <c r="J15" s="8" t="n">
+        <v>783</v>
+      </c>
+      <c r="K15" s="8" t="n"/>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="n">
+        <v>25</v>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="n"/>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>kg/m2</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="n"/>
+      <c r="V15" s="8" t="n"/>
+      <c r="W15" s="8" t="n"/>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t>95.0 – 125.0</t>
+        </is>
+      </c>
+      <c r="Y15" s="8" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="Z15" s="8" t="n"/>
+      <c r="AA15" s="8" t="n"/>
+      <c r="AB15" s="8" t="n"/>
+      <c r="AC15" s="8" t="inlineStr">
+        <is>
+          <t>140.0 – 199.0</t>
+        </is>
+      </c>
+      <c r="AD15" s="8" t="inlineStr">
+        <is>
+          <t>mg/dL</t>
+        </is>
+      </c>
+      <c r="AE15" s="8" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AF15" s="8" t="inlineStr">
+        <is>
+          <t>Overall</t>
+        </is>
+      </c>
+      <c r="AG15" s="8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH15" s="8" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="AI15" s="8" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AJ15" s="8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AK15" s="8" t="n"/>
+      <c r="AL15" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AM15" s="8" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="AN15" s="8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AO15" s="8" t="n"/>
+      <c r="AP15" s="8" t="inlineStr">
+        <is>
+          <t>cm</t>
+        </is>
+      </c>
+      <c r="AQ15" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR15" s="8" t="n"/>
+      <c r="AS15" s="8" t="n"/>
+      <c r="AT15" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="AU15" s="8" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="AV15" s="8" t="n"/>
+      <c r="AW15" s="8" t="n"/>
+      <c r="AX15" s="8" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="AI1:AX1"/>
+    <mergeCell ref="AU2:AX2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="U2:Y2"/>
+    <mergeCell ref="Z2:AD2"/>
+    <mergeCell ref="K2:O2"/>
+    <mergeCell ref="AG2:AH2"/>
+    <mergeCell ref="AM2:AP2"/>
+    <mergeCell ref="AQ2:AT2"/>
+    <mergeCell ref="P2:T2"/>
+    <mergeCell ref="K1:AD1"/>
+    <mergeCell ref="AI2:AL2"/>
+    <mergeCell ref="AE1:AH1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -468,118 +2869,118 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>authors</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>publication_year</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>journal</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>doi</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>study_design</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>study_phase</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>total_sample_size</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>duration_value</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>duration_unit</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>condition_studied</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Long-Term Safety, Tolerability, and Weight Loss Associated With Metformin in the Diabetes Prevention Program Outcomes Study</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>DPP Research Group</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="10" t="n">
         <v>2012</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>Diabetes Care</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>10.2337/dc11-1299</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>Multicenter randomized placebo-controlled clinical trial</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>DPP 2-year double-blind phase + DPPOS follow-up</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="10" t="n">
         <v>2155</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="K2" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="L2" s="10" t="inlineStr">
         <is>
           <t>Prediabetes / Impaired Glucose Tolerance</t>
         </is>
@@ -590,7 +2991,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -614,162 +3015,162 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>arm_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>arm_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>intervention_type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>drug_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>dose_value</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>dose_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>frequency_number</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>frequency_unit</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>sample_size_allocated</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>sample_size_analyzed</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>source_page</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_850</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>experimental</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>Metformin</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="10" t="n">
         <v>850</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>mg</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
         <is>
           <t>twice daily</t>
         </is>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="10" t="n">
         <v>790</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="10" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_PLA</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="n"/>
-      <c r="H3" s="2" t="n">
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t>twice daily</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="10" t="n">
         <v>783</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -778,7 +3179,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -805,303 +3206,303 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>criterion_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>criterion_type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>criterion_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>less_than (&lt;)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>equal (=)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>greater_than (&gt;)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>between</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>min_value</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>max_value</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>raw_source_text</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>source_page</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>ELIG_001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>inclusion</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>demographic</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n"/>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>&gt;</t>
         </is>
       </c>
-      <c r="I2" s="2" t="n"/>
-      <c r="J2" s="2" t="n">
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>age &gt;= 25 years</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="10" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ELIG_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>inclusion</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>demographic</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>bmi</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n"/>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>&gt;</t>
         </is>
       </c>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n">
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="inlineStr">
         <is>
           <t>kg/m2</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>BMI &gt;= 24 kg/m2</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="10" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>ELIG_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>inclusion</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>biomarker</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>baseline_fasting_glucose</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n"/>
-      <c r="G4" s="2" t="n"/>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="10" t="n"/>
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>between</t>
         </is>
       </c>
-      <c r="J4" s="2" t="n"/>
-      <c r="K4" s="2" t="n">
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n">
         <v>95</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>fasting plasma glucose 95–125 mg/dL</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="10" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>ELIG_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>inclusion</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>biomarker</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>baseline_impaired_glucose_tolerance</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>between</t>
         </is>
       </c>
-      <c r="J5" s="2" t="n"/>
-      <c r="K5" s="2" t="n">
+      <c r="J5" s="10" t="n"/>
+      <c r="K5" s="10" t="n">
         <v>140</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="10" t="n">
         <v>199</v>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="10" t="inlineStr">
         <is>
           <t>mg/dL</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>impaired glucose tolerance 140–199 mg/dL</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1110,7 +3511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1146,1586 +3547,1586 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>outcome_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>arm_id</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>race</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>domain</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>parameter_name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>statistical_type</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Timepoint (value)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Timepoint (unit)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>sample_size</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>mean</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>sd</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>change_value</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>change_sd</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>events</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" s="9" t="inlineStr">
         <is>
           <t>percentage</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" s="9" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" s="9" t="inlineStr">
         <is>
           <t>effect_measure</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" s="9" t="inlineStr">
         <is>
           <t>effect_value</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" s="9" t="inlineStr">
         <is>
           <t>p_value</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" s="9" t="inlineStr">
         <is>
           <t>source_page</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" s="9" t="inlineStr">
         <is>
           <t>source_location</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" s="9" t="inlineStr">
         <is>
           <t>raw_source_text</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>OUT_001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_850</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>anthropometric</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>Weight Loss</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="10" t="n">
         <v>5.7</v>
       </c>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n">
+      <c r="V2" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="W2" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 2</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="X2" s="10" t="inlineStr">
         <is>
           <t>mean weight loss was 2.1 ± 5.7% in metformin vs placebo</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>OUT_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_PLA</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>anthropometric</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>Weight Loss</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="10" t="n">
         <v>0.43</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="10" t="n">
         <v>4.7</v>
       </c>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
-      <c r="O3" s="2" t="n"/>
-      <c r="P3" s="2" t="n"/>
-      <c r="Q3" s="2" t="n"/>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S3" s="2" t="n"/>
-      <c r="T3" s="2" t="n"/>
-      <c r="U3" s="2" t="n"/>
-      <c r="V3" s="2" t="n">
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="W3" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 2</t>
         </is>
       </c>
-      <c r="X3" s="2" t="inlineStr">
+      <c r="X3" s="10" t="inlineStr">
         <is>
           <t>0.43 ± 4.7% in the placebo group</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>OUT_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_850</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>anthropometric</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Waist Circumference Reduction</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="10" t="n">
         <v>7.1</v>
       </c>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n"/>
-      <c r="P4" s="2" t="n"/>
-      <c r="Q4" s="2" t="n"/>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="inlineStr">
         <is>
           <t>cm</t>
         </is>
       </c>
-      <c r="S4" s="2" t="n"/>
-      <c r="T4" s="2" t="n"/>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="V4" s="2" t="n">
+      <c r="V4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W4" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 2</t>
         </is>
       </c>
-      <c r="X4" s="2" t="inlineStr">
+      <c r="X4" s="10" t="inlineStr">
         <is>
           <t>reduced at 2 years by 2.1 ± 7.1 cm in metformin group</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>OUT_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_PLA</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>anthropometric</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>Waist Circumference Reduction</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>continuous</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="10" t="n">
         <v>0.79</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="n"/>
-      <c r="O5" s="2" t="n"/>
-      <c r="P5" s="2" t="n"/>
-      <c r="Q5" s="2" t="n"/>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="n"/>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="inlineStr">
         <is>
           <t>cm</t>
         </is>
       </c>
-      <c r="S5" s="2" t="n"/>
-      <c r="T5" s="2" t="n"/>
-      <c r="U5" s="2" t="n"/>
-      <c r="V5" s="2" t="n">
+      <c r="S5" s="10" t="n"/>
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="10" t="n"/>
+      <c r="V5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W5" s="2" t="inlineStr">
+      <c r="W5" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 2</t>
         </is>
       </c>
-      <c r="X5" s="2" t="inlineStr">
+      <c r="X5" s="10" t="inlineStr">
         <is>
           <t>0.79 ± 6.5 cm in the placebo group</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>OUT_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_850</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>anthropometric</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>Weight Loss &gt;= 5%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="n">
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n"/>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="n"/>
-      <c r="P6" s="2" t="n">
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="Q6" s="2" t="n">
+      <c r="Q6" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="R6" s="2" t="inlineStr">
+      <c r="R6" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S6" s="2" t="n"/>
-      <c r="T6" s="2" t="n"/>
-      <c r="U6" s="2" t="inlineStr">
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="inlineStr">
         <is>
           <t>&lt;0.001</t>
         </is>
       </c>
-      <c r="V6" s="2" t="n">
+      <c r="V6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 3</t>
         </is>
       </c>
-      <c r="X6" s="2" t="inlineStr">
+      <c r="X6" s="10" t="inlineStr">
         <is>
           <t>26% of metformin lost &gt;= 5% body weight</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>OUT_006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_PLA</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>anthropometric</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>Weight Loss &gt;= 5%</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="n">
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="n"/>
-      <c r="O7" s="2" t="n"/>
-      <c r="P7" s="2" t="n">
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n"/>
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="Q7" s="2" t="n">
+      <c r="Q7" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="R7" s="2" t="inlineStr">
+      <c r="R7" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S7" s="2" t="n"/>
-      <c r="T7" s="2" t="n"/>
-      <c r="U7" s="2" t="n"/>
-      <c r="V7" s="2" t="n">
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 3</t>
         </is>
       </c>
-      <c r="X7" s="2" t="inlineStr">
+      <c r="X7" s="10" t="inlineStr">
         <is>
           <t>14% of placebo group had lost &gt;= 5%</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>OUT_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_850</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="n"/>
-      <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n">
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n">
         <v>26.5</v>
       </c>
-      <c r="R8" s="2" t="inlineStr">
+      <c r="R8" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S8" s="2" t="n"/>
-      <c r="T8" s="2" t="n"/>
-      <c r="U8" s="2" t="n"/>
-      <c r="V8" s="2" t="n">
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="n"/>
+      <c r="V8" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="W8" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="X8" s="2" t="inlineStr">
+      <c r="X8" s="10" t="inlineStr">
         <is>
           <t>Overall Metformin High Adherence 26.5%</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>OUT_008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_PLA</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n">
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
-      <c r="O9" s="2" t="n"/>
-      <c r="P9" s="2" t="n"/>
-      <c r="Q9" s="2" t="n">
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n"/>
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n">
         <v>6.9</v>
       </c>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="R9" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S9" s="2" t="n"/>
-      <c r="T9" s="2" t="n"/>
-      <c r="U9" s="2" t="n"/>
-      <c r="V9" s="2" t="n">
+      <c r="S9" s="10" t="n"/>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="n"/>
+      <c r="V9" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W9" s="2" t="inlineStr">
+      <c r="W9" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="X9" s="2" t="inlineStr">
+      <c r="X9" s="10" t="inlineStr">
         <is>
           <t>Overall Placebo High Adherence 6.9%</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>OUT_009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_850</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Caucasian</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="n">
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n"/>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="2" t="n"/>
-      <c r="P10" s="2" t="n"/>
-      <c r="Q10" s="2" t="n">
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="10" t="n">
         <v>29.7</v>
       </c>
-      <c r="R10" s="2" t="inlineStr">
+      <c r="R10" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S10" s="2" t="n"/>
-      <c r="T10" s="2" t="n"/>
-      <c r="U10" s="2" t="n"/>
-      <c r="V10" s="2" t="n">
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="10" t="n"/>
+      <c r="V10" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="W10" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="X10" s="2" t="inlineStr">
+      <c r="X10" s="10" t="inlineStr">
         <is>
           <t>Caucasian Metformin High Adherence 29.7%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>OUT_010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_PLA</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Caucasian</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="n">
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n"/>
-      <c r="P11" s="2" t="n"/>
-      <c r="Q11" s="2" t="n">
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n"/>
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="n"/>
+      <c r="Q11" s="10" t="n">
         <v>7.8</v>
       </c>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="R11" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S11" s="2" t="n"/>
-      <c r="T11" s="2" t="n"/>
-      <c r="U11" s="2" t="n"/>
-      <c r="V11" s="2" t="n">
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="10" t="n"/>
+      <c r="V11" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W11" s="2" t="inlineStr">
+      <c r="W11" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="X11" s="2" t="inlineStr">
+      <c r="X11" s="10" t="inlineStr">
         <is>
           <t>Caucasian Placebo High Adherence 7.8%</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>OUT_011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_850</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>African American</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="n">
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n"/>
-      <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n">
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="R12" s="2" t="inlineStr">
+      <c r="R12" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S12" s="2" t="n"/>
-      <c r="T12" s="2" t="n"/>
-      <c r="U12" s="2" t="n"/>
-      <c r="V12" s="2" t="n">
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="n"/>
+      <c r="V12" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="W12" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="X12" s="2" t="inlineStr">
+      <c r="X12" s="10" t="inlineStr">
         <is>
           <t>African American Metformin High Adherence 17.2%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>OUT_012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_PLA</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>African American</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="n">
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n"/>
-      <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n">
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n"/>
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n">
         <v>5.9</v>
       </c>
-      <c r="R13" s="2" t="inlineStr">
+      <c r="R13" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S13" s="2" t="n"/>
-      <c r="T13" s="2" t="n"/>
-      <c r="U13" s="2" t="n"/>
-      <c r="V13" s="2" t="n">
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="10" t="n"/>
+      <c r="V13" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W13" s="2" t="inlineStr">
+      <c r="W13" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="X13" s="2" t="inlineStr">
+      <c r="X13" s="10" t="inlineStr">
         <is>
           <t>African American Placebo High Adherence 5.9%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>OUT_013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_850</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>Hispanic</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="n">
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n"/>
-      <c r="P14" s="2" t="n"/>
-      <c r="Q14" s="2" t="n">
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R14" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S14" s="2" t="n"/>
-      <c r="T14" s="2" t="n"/>
-      <c r="U14" s="2" t="n"/>
-      <c r="V14" s="2" t="n">
+      <c r="S14" s="10" t="n"/>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="10" t="n"/>
+      <c r="V14" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="W14" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="X14" s="2" t="inlineStr">
+      <c r="X14" s="10" t="inlineStr">
         <is>
           <t>Hispanic Metformin High Adherence 28.4%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>OUT_014</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_PLA</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>Hispanic</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="n">
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="n"/>
-      <c r="O15" s="2" t="n"/>
-      <c r="P15" s="2" t="n"/>
-      <c r="Q15" s="2" t="n">
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="10" t="n"/>
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="10" t="n"/>
+      <c r="O15" s="10" t="n"/>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="R15" s="2" t="inlineStr">
+      <c r="R15" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S15" s="2" t="n"/>
-      <c r="T15" s="2" t="n"/>
-      <c r="U15" s="2" t="n"/>
-      <c r="V15" s="2" t="n">
+      <c r="S15" s="10" t="n"/>
+      <c r="T15" s="10" t="n"/>
+      <c r="U15" s="10" t="n"/>
+      <c r="V15" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="W15" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="X15" s="2" t="inlineStr">
+      <c r="X15" s="10" t="inlineStr">
         <is>
           <t>Hispanic Placebo High Adherence 6.5%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>OUT_015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_850</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>Asian</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n"/>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="n"/>
-      <c r="O16" s="2" t="n"/>
-      <c r="P16" s="2" t="n"/>
-      <c r="Q16" s="2" t="n">
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="10" t="n"/>
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="10" t="n"/>
+      <c r="O16" s="10" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R16" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S16" s="2" t="n"/>
-      <c r="T16" s="2" t="n"/>
-      <c r="U16" s="2" t="n"/>
-      <c r="V16" s="2" t="n">
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="10" t="n"/>
+      <c r="U16" s="10" t="n"/>
+      <c r="V16" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="W16" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="X16" s="2" t="inlineStr">
+      <c r="X16" s="10" t="inlineStr">
         <is>
           <t>Asian Metformin High Adherence 25.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>OUT_016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_PLA</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Asian</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n"/>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="n"/>
-      <c r="O17" s="2" t="n"/>
-      <c r="P17" s="2" t="n"/>
-      <c r="Q17" s="2" t="n">
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="10" t="n"/>
+      <c r="M17" s="10" t="n"/>
+      <c r="N17" s="10" t="n"/>
+      <c r="O17" s="10" t="n"/>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R17" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S17" s="2" t="n"/>
-      <c r="T17" s="2" t="n"/>
-      <c r="U17" s="2" t="n"/>
-      <c r="V17" s="2" t="n">
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="10" t="n"/>
+      <c r="U17" s="10" t="n"/>
+      <c r="V17" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W17" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
+      <c r="X17" s="10" t="inlineStr">
         <is>
           <t>Asian Placebo High Adherence 8.2%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>OUT_017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_850</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Native American</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="n">
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="n"/>
-      <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n">
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="10" t="n"/>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="10" t="n"/>
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="R18" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S18" s="2" t="n"/>
-      <c r="T18" s="2" t="n"/>
-      <c r="U18" s="2" t="n"/>
-      <c r="V18" s="2" t="n">
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="n"/>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="W18" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="X18" s="2" t="inlineStr">
+      <c r="X18" s="10" t="inlineStr">
         <is>
           <t>Native American Metformin High Adherence 23.1%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>OUT_018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_PLA</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Native American</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>dichotomous</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="n">
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="n"/>
-      <c r="O19" s="2" t="n"/>
-      <c r="P19" s="2" t="n"/>
-      <c r="Q19" s="2" t="n">
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n"/>
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="n"/>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n">
         <v>1.7</v>
       </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="R19" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="S19" s="2" t="n"/>
-      <c r="T19" s="2" t="n"/>
-      <c r="U19" s="2" t="n"/>
-      <c r="V19" s="2" t="n">
+      <c r="S19" s="10" t="n"/>
+      <c r="T19" s="10" t="n"/>
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="W19" s="2" t="inlineStr">
+      <c r="W19" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="X19" s="2" t="inlineStr">
+      <c r="X19" s="10" t="inlineStr">
         <is>
           <t>Native American Placebo High Adherence 1.7%</t>
         </is>
@@ -2736,7 +5137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2756,1002 +5157,1002 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>provenance_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>target_entity</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>target_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>field_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>source_page</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>source_location</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>exact_source_text</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>PROV_001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Studies</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="10" t="inlineStr">
         <is>
           <t>Title Header</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>Long-Term Safety, Tolerability, and Weight Loss Associated With Metformin in the Diabetes Prevention Program Outcomes Study</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>PROV_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Arms</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>ARM_MET_850</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>dose_value</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="F3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t>Methods - Intervention</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg: 850.0 mg 2.0 twice daily</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>PROV_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Eligibility</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>ELIG_001</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Methods - Eligibility criteria</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>age &gt;= 25 years</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>PROV_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Eligibility</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>ELIG_002</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>bmi</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
+      <c r="F5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Methods - Eligibility criteria</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>BMI &gt;= 24 kg/m2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>PROV_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Eligibility</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>ELIG_003</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>baseline_fasting_glucose</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
+      <c r="F6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Methods - Eligibility criteria</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>fasting plasma glucose 95–125 mg/dL</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>PROV_006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Eligibility</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>ELIG_004</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>baseline_impaired_glucose_tolerance</t>
         </is>
       </c>
-      <c r="F7" s="2" t="n">
+      <c r="F7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Methods - Eligibility criteria</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>impaired glucose tolerance 140–199 mg/dL</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>PROV_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>OUT_001</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>Weight Loss</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
+      <c r="F8" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 2</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>mean weight loss was 2.1 ± 5.7% in metformin vs placebo</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>PROV_008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>OUT_002</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Weight Loss</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
+      <c r="F9" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 2</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>0.43 ± 4.7% in the placebo group</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>PROV_009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>OUT_003</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Waist Circumference Reduction</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
+      <c r="F10" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 2</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>reduced at 2 years by 2.1 ± 7.1 cm in metformin group</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>PROV_010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>OUT_004</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>Waist Circumference Reduction</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
+      <c r="F11" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 2</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>0.79 ± 6.5 cm in the placebo group</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>PROV_011</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>OUT_005</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>Weight Loss &gt;= 5%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="n">
+      <c r="F12" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 3</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>26% of metformin lost &gt;= 5% body weight</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>PROV_012</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>OUT_006</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>Weight Loss &gt;= 5%</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
+      <c r="F13" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 3</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>14% of placebo group had lost &gt;= 5%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>PROV_013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>OUT_007</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
+      <c r="F14" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Overall Metformin High Adherence 26.5%</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>PROV_014</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>OUT_008</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="F15" s="2" t="n">
+      <c r="F15" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Overall Placebo High Adherence 6.9%</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>PROV_015</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>OUT_009</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
+      <c r="F16" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Caucasian Metformin High Adherence 29.7%</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>PROV_016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>OUT_010</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
+      <c r="F17" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>Caucasian Placebo High Adherence 7.8%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>PROV_017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>OUT_011</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="F18" s="2" t="n">
+      <c r="F18" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>African American Metformin High Adherence 17.2%</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>PROV_018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>OUT_012</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="F19" s="2" t="n">
+      <c r="F19" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>African American Placebo High Adherence 5.9%</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>PROV_019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>OUT_013</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="F20" s="2" t="n">
+      <c r="F20" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>Hispanic Metformin High Adherence 28.4%</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="10" t="inlineStr">
         <is>
           <t>PROV_020</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>OUT_014</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="F21" s="2" t="n">
+      <c r="F21" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Hispanic Placebo High Adherence 6.5%</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="10" t="inlineStr">
         <is>
           <t>PROV_021</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="10" t="inlineStr">
         <is>
           <t>OUT_015</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
+      <c r="F22" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>Asian Metformin High Adherence 25.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>PROV_022</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="D23" s="10" t="inlineStr">
         <is>
           <t>OUT_016</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E23" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="F23" s="2" t="n">
+      <c r="F23" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Asian Placebo High Adherence 8.2%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="10" t="inlineStr">
         <is>
           <t>PROV_023</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="10" t="inlineStr">
         <is>
           <t>OUT_017</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="F24" s="2" t="n">
+      <c r="F24" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>Native American Metformin High Adherence 23.1%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>PROV_024</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>Outcomes</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="10" t="inlineStr">
         <is>
           <t>OUT_018</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="F25" s="2" t="n">
+      <c r="F25" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>Native American Placebo High Adherence 1.7%</t>
         </is>
@@ -3762,7 +6163,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3782,42 +6183,42 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>issue_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>target_entity</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>target_id</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>field_name</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>issue_type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>review_required</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
@@ -3828,7 +6229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3856,1314 +6257,1314 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>arm_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>race</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>intervention_type</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>dose</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>sample_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Timepoint (value)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Timepoint (unit)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>parameter_name</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" s="9" t="inlineStr">
         <is>
           <t>mean_or_events</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" s="9" t="inlineStr">
         <is>
           <t>sd_or_pct</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" s="9" t="inlineStr">
         <is>
           <t>change</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" s="9" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" s="9" t="inlineStr">
         <is>
           <t>source_page</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" s="9" t="inlineStr">
         <is>
           <t>source_location</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="10" t="inlineStr">
         <is>
           <t>experimental</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>850.0 mg</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J2" s="10" t="inlineStr">
         <is>
           <t>Weight Loss</t>
         </is>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" s="10" t="n">
         <v>5.7</v>
       </c>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
+      <c r="O2" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="P2" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 2</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="10" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="G3" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J3" s="10" t="inlineStr">
         <is>
           <t>Weight Loss</t>
         </is>
       </c>
-      <c r="K3" s="2" t="n">
+      <c r="K3" s="10" t="n">
         <v>0.43</v>
       </c>
-      <c r="L3" s="2" t="n">
+      <c r="L3" s="10" t="n">
         <v>4.7</v>
       </c>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
+      <c r="O3" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 2</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>experimental</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>850.0 mg</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G4" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Waist Circumference Reduction</t>
         </is>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K4" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L4" s="10" t="n">
         <v>7.1</v>
       </c>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>cm</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
+      <c r="O4" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="P4" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 2</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="10" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G5" s="2" t="n">
+      <c r="G5" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
         <is>
           <t>Waist Circumference Reduction</t>
         </is>
       </c>
-      <c r="K5" s="2" t="n">
+      <c r="K5" s="10" t="n">
         <v>0.79</v>
       </c>
-      <c r="L5" s="2" t="n">
+      <c r="L5" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="M5" s="2" t="n"/>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="M5" s="10" t="n"/>
+      <c r="N5" s="10" t="inlineStr">
         <is>
           <t>cm</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="O5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 2</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>experimental</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>850.0 mg</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G6" s="2" t="n">
+      <c r="G6" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
         <is>
           <t>Weight Loss &gt;= 5%</t>
         </is>
       </c>
-      <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="n">
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="M6" s="2" t="n"/>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="O6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 3</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G7" s="2" t="n">
+      <c r="G7" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>Weight Loss &gt;= 5%</t>
         </is>
       </c>
-      <c r="K7" s="2" t="n"/>
-      <c r="L7" s="2" t="n">
+      <c r="K7" s="10" t="n"/>
+      <c r="L7" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="M7" s="2" t="n"/>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="M7" s="10" t="n"/>
+      <c r="N7" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
+      <c r="O7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P7" s="10" t="inlineStr">
         <is>
           <t>Results paragraph 3</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>experimental</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>850.0 mg</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G8" s="2" t="n">
+      <c r="G8" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n">
+      <c r="K8" s="10" t="n"/>
+      <c r="L8" s="10" t="n">
         <v>26.5</v>
       </c>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
+      <c r="O8" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="P8" s="2" t="inlineStr">
+      <c r="P8" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G9" s="2" t="n">
+      <c r="G9" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n">
+      <c r="K9" s="10" t="n"/>
+      <c r="L9" s="10" t="n">
         <v>6.9</v>
       </c>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="M9" s="10" t="n"/>
+      <c r="N9" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
+      <c r="O9" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Caucasian</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>experimental</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>850.0 mg</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G10" s="2" t="n">
+      <c r="G10" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="2" t="n">
+      <c r="K10" s="10" t="n"/>
+      <c r="L10" s="10" t="n">
         <v>29.7</v>
       </c>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
+      <c r="O10" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="P10" s="2" t="inlineStr">
+      <c r="P10" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Caucasian</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
+      <c r="G11" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n">
+      <c r="K11" s="10" t="n"/>
+      <c r="L11" s="10" t="n">
         <v>7.8</v>
       </c>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="M11" s="10" t="n"/>
+      <c r="N11" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="n">
+      <c r="O11" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P11" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>African American</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>experimental</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>850.0 mg</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G12" s="2" t="n">
+      <c r="G12" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n">
+      <c r="K12" s="10" t="n"/>
+      <c r="L12" s="10" t="n">
         <v>17.2</v>
       </c>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O12" s="2" t="n">
+      <c r="O12" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="P12" s="2" t="inlineStr">
+      <c r="P12" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>African American</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G13" s="2" t="n">
+      <c r="G13" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n">
+      <c r="K13" s="10" t="n"/>
+      <c r="L13" s="10" t="n">
         <v>5.9</v>
       </c>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="M13" s="10" t="n"/>
+      <c r="N13" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="n">
+      <c r="O13" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="P13" s="2" t="inlineStr">
+      <c r="P13" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>Hispanic</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="10" t="inlineStr">
         <is>
           <t>experimental</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="10" t="inlineStr">
         <is>
           <t>850.0 mg</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G14" s="2" t="n">
+      <c r="G14" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n">
+      <c r="K14" s="10" t="n"/>
+      <c r="L14" s="10" t="n">
         <v>28.4</v>
       </c>
-      <c r="M14" s="2" t="n"/>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="n">
+      <c r="O14" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>Hispanic</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="10" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G15" s="2" t="n">
+      <c r="G15" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="K15" s="2" t="n"/>
-      <c r="L15" s="2" t="n">
+      <c r="K15" s="10" t="n"/>
+      <c r="L15" s="10" t="n">
         <v>6.5</v>
       </c>
-      <c r="M15" s="2" t="n"/>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="M15" s="10" t="n"/>
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O15" s="2" t="n">
+      <c r="O15" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="P15" s="2" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>Asian</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="10" t="inlineStr">
         <is>
           <t>experimental</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>850.0 mg</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G16" s="2" t="n">
+      <c r="G16" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="K16" s="2" t="n"/>
-      <c r="L16" s="2" t="n">
+      <c r="K16" s="10" t="n"/>
+      <c r="L16" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="M16" s="2" t="n"/>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="n">
+      <c r="O16" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P16" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>Asian</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G17" s="2" t="n">
+      <c r="G17" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="K17" s="2" t="n"/>
-      <c r="L17" s="2" t="n">
+      <c r="K17" s="10" t="n"/>
+      <c r="L17" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="M17" s="2" t="n"/>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="M17" s="10" t="n"/>
+      <c r="N17" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O17" s="2" t="n">
+      <c r="O17" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P17" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>Native American</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>experimental</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="10" t="inlineStr">
         <is>
           <t>850.0 mg</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G18" s="2" t="n">
+      <c r="G18" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n">
+      <c r="K18" s="10" t="n"/>
+      <c r="L18" s="10" t="n">
         <v>23.1</v>
       </c>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="n">
+      <c r="O18" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="P18" s="2" t="inlineStr">
+      <c r="P18" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>Native American</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>placebo</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>2.0 twice daily</t>
         </is>
       </c>
-      <c r="G19" s="2" t="n">
+      <c r="G19" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="J19" s="10" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n">
+      <c r="K19" s="10" t="n"/>
+      <c r="L19" s="10" t="n">
         <v>1.7</v>
       </c>
-      <c r="M19" s="2" t="n"/>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="M19" s="10" t="n"/>
+      <c r="N19" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="n">
+      <c r="O19" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="P19" s="2" t="inlineStr">
+      <c r="P19" s="10" t="inlineStr">
         <is>
           <t>Table 1</t>
         </is>
@@ -5174,7 +7575,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5196,498 +7597,498 @@
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>study_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="9" t="inlineStr">
         <is>
           <t>arm_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="9" t="inlineStr">
         <is>
           <t>race</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="9" t="inlineStr">
         <is>
           <t>sample_size</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="9" t="inlineStr">
         <is>
           <t>Timepoint (value)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="9" t="inlineStr">
         <is>
           <t>Timepoint (unit)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="9" t="inlineStr">
         <is>
           <t>Weight Loss (%)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="9" t="inlineStr">
         <is>
           <t>Waist Circumference Reduction (cm)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="9" t="inlineStr">
         <is>
           <t>Weight Loss &gt;= 5% (%)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" s="9" t="inlineStr">
         <is>
           <t>High Adherence (%)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="n">
+      <c r="F2" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" s="10" t="n">
         <v>2.1</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" s="10" t="n">
         <v>26.5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="n">
+      <c r="F3" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G3" s="10" t="n">
         <v>0.43</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="H3" s="10" t="n">
         <v>0.79</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" s="10" t="n">
         <v>6.9</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Caucasian</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="n">
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr"/>
+      <c r="H4" s="10" t="inlineStr"/>
+      <c r="I4" s="10" t="inlineStr"/>
+      <c r="J4" s="10" t="n">
         <v>29.7</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>Caucasian</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="n">
+      <c r="F5" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr"/>
+      <c r="H5" s="10" t="inlineStr"/>
+      <c r="I5" s="10" t="inlineStr"/>
+      <c r="J5" s="10" t="n">
         <v>7.8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>African American</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="n">
+      <c r="F6" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr"/>
+      <c r="H6" s="10" t="inlineStr"/>
+      <c r="I6" s="10" t="inlineStr"/>
+      <c r="J6" s="10" t="n">
         <v>17.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>African American</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="n">
+      <c r="F7" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr"/>
+      <c r="H7" s="10" t="inlineStr"/>
+      <c r="I7" s="10" t="inlineStr"/>
+      <c r="J7" s="10" t="n">
         <v>5.9</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Hispanic</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="n">
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr"/>
+      <c r="H8" s="10" t="inlineStr"/>
+      <c r="I8" s="10" t="inlineStr"/>
+      <c r="J8" s="10" t="n">
         <v>28.4</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Hispanic</t>
         </is>
       </c>
-      <c r="D9" s="2" t="n">
+      <c r="D9" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="n">
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr"/>
+      <c r="H9" s="10" t="inlineStr"/>
+      <c r="I9" s="10" t="inlineStr"/>
+      <c r="J9" s="10" t="n">
         <v>6.5</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Asian</t>
         </is>
       </c>
-      <c r="D10" s="2" t="n">
+      <c r="D10" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="n">
+      <c r="F10" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr"/>
+      <c r="H10" s="10" t="inlineStr"/>
+      <c r="I10" s="10" t="inlineStr"/>
+      <c r="J10" s="10" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Asian</t>
         </is>
       </c>
-      <c r="D11" s="2" t="n">
+      <c r="D11" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="n">
+      <c r="F11" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr"/>
+      <c r="H11" s="10" t="inlineStr"/>
+      <c r="I11" s="10" t="inlineStr"/>
+      <c r="J11" s="10" t="n">
         <v>8.199999999999999</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Metformin 850mg</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Native American</t>
         </is>
       </c>
-      <c r="D12" s="2" t="n">
+      <c r="D12" s="10" t="n">
         <v>1073</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="n">
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr"/>
+      <c r="H12" s="10" t="inlineStr"/>
+      <c r="I12" s="10" t="inlineStr"/>
+      <c r="J12" s="10" t="n">
         <v>23.1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>RCT_METFORMIN_2012</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>RCT_METFORMIN_2012</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Placebo</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>Native American</t>
         </is>
       </c>
-      <c r="D13" s="2" t="n">
+      <c r="D13" s="10" t="n">
         <v>1082</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>years</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="n">
+      <c r="F13" s="10" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="G13" s="10" t="inlineStr"/>
+      <c r="H13" s="10" t="inlineStr"/>
+      <c r="I13" s="10" t="inlineStr"/>
+      <c r="J13" s="10" t="n">
         <v>1.7</v>
       </c>
     </row>

--- a/outputs/metformin_structured_extracted.xlsx
+++ b/outputs/metformin_structured_extracted.xlsx
@@ -94,7 +94,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -116,11 +116,55 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -148,6 +192,8 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -222,6 +268,276 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>51</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>13</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>16</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>25</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>9</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>17</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>11</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="476250" cy="476250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -574,67 +890,67 @@
           <t>STUDY &amp; INTERVENTION ARMS</t>
         </is>
       </c>
-      <c r="B1" s="1" t="n"/>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
+      <c r="B1" s="11" t="n"/>
+      <c r="C1" s="11" t="n"/>
+      <c r="D1" s="11" t="n"/>
+      <c r="E1" s="11" t="n"/>
+      <c r="F1" s="11" t="n"/>
+      <c r="G1" s="11" t="n"/>
+      <c r="H1" s="11" t="n"/>
+      <c r="I1" s="11" t="n"/>
+      <c r="J1" s="12" t="n"/>
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>ELIGIBILITY CRITERIA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
-      <c r="T1" s="1" t="n"/>
-      <c r="U1" s="1" t="n"/>
-      <c r="V1" s="1" t="n"/>
-      <c r="W1" s="1" t="n"/>
-      <c r="X1" s="1" t="n"/>
-      <c r="Y1" s="1" t="n"/>
-      <c r="Z1" s="1" t="n"/>
-      <c r="AA1" s="1" t="n"/>
-      <c r="AB1" s="1" t="n"/>
-      <c r="AC1" s="1" t="n"/>
-      <c r="AD1" s="1" t="n"/>
+      <c r="L1" s="11" t="n"/>
+      <c r="M1" s="11" t="n"/>
+      <c r="N1" s="11" t="n"/>
+      <c r="O1" s="11" t="n"/>
+      <c r="P1" s="11" t="n"/>
+      <c r="Q1" s="11" t="n"/>
+      <c r="R1" s="11" t="n"/>
+      <c r="S1" s="11" t="n"/>
+      <c r="T1" s="11" t="n"/>
+      <c r="U1" s="11" t="n"/>
+      <c r="V1" s="11" t="n"/>
+      <c r="W1" s="11" t="n"/>
+      <c r="X1" s="11" t="n"/>
+      <c r="Y1" s="11" t="n"/>
+      <c r="Z1" s="11" t="n"/>
+      <c r="AA1" s="11" t="n"/>
+      <c r="AB1" s="11" t="n"/>
+      <c r="AC1" s="11" t="n"/>
+      <c r="AD1" s="12" t="n"/>
       <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>POPULATION STRATIFICATION</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="n"/>
-      <c r="AG1" s="1" t="n"/>
-      <c r="AH1" s="1" t="n"/>
+      <c r="AF1" s="11" t="n"/>
+      <c r="AG1" s="11" t="n"/>
+      <c r="AH1" s="12" t="n"/>
       <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>CLINICAL VARIABLES &amp; OUTCOMES</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="n"/>
-      <c r="AK1" s="1" t="n"/>
-      <c r="AL1" s="1" t="n"/>
-      <c r="AM1" s="1" t="n"/>
-      <c r="AN1" s="1" t="n"/>
-      <c r="AO1" s="1" t="n"/>
-      <c r="AP1" s="1" t="n"/>
-      <c r="AQ1" s="1" t="n"/>
-      <c r="AR1" s="1" t="n"/>
-      <c r="AS1" s="1" t="n"/>
-      <c r="AT1" s="1" t="n"/>
-      <c r="AU1" s="1" t="n"/>
-      <c r="AV1" s="1" t="n"/>
-      <c r="AW1" s="1" t="n"/>
-      <c r="AX1" s="1" t="n"/>
+      <c r="AJ1" s="11" t="n"/>
+      <c r="AK1" s="11" t="n"/>
+      <c r="AL1" s="11" t="n"/>
+      <c r="AM1" s="11" t="n"/>
+      <c r="AN1" s="11" t="n"/>
+      <c r="AO1" s="11" t="n"/>
+      <c r="AP1" s="11" t="n"/>
+      <c r="AQ1" s="11" t="n"/>
+      <c r="AR1" s="11" t="n"/>
+      <c r="AS1" s="11" t="n"/>
+      <c r="AT1" s="11" t="n"/>
+      <c r="AU1" s="11" t="n"/>
+      <c r="AV1" s="11" t="n"/>
+      <c r="AW1" s="11" t="n"/>
+      <c r="AX1" s="12" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -672,7 +988,7 @@
           <t>Period of Study</t>
         </is>
       </c>
-      <c r="H2" s="2" t="n"/>
+      <c r="H2" s="12" t="n"/>
       <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Total Cohort (N)</t>
@@ -688,37 +1004,37 @@
           <t>Age</t>
         </is>
       </c>
-      <c r="L2" s="2" t="n"/>
-      <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n"/>
+      <c r="L2" s="11" t="n"/>
+      <c r="M2" s="11" t="n"/>
+      <c r="N2" s="11" t="n"/>
+      <c r="O2" s="12" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Bmi</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
+      <c r="Q2" s="11" t="n"/>
+      <c r="R2" s="11" t="n"/>
+      <c r="S2" s="11" t="n"/>
+      <c r="T2" s="12" t="n"/>
       <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Baseline Fasting Glucose</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n"/>
-      <c r="W2" s="2" t="n"/>
-      <c r="X2" s="2" t="n"/>
-      <c r="Y2" s="2" t="n"/>
+      <c r="V2" s="11" t="n"/>
+      <c r="W2" s="11" t="n"/>
+      <c r="X2" s="11" t="n"/>
+      <c r="Y2" s="12" t="n"/>
       <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>Baseline Impaired Glucose Tolerance</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="n"/>
-      <c r="AB2" s="2" t="n"/>
-      <c r="AC2" s="2" t="n"/>
-      <c r="AD2" s="2" t="n"/>
+      <c r="AA2" s="11" t="n"/>
+      <c r="AB2" s="11" t="n"/>
+      <c r="AC2" s="11" t="n"/>
+      <c r="AD2" s="12" t="n"/>
       <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>Race / Ethnicity</t>
@@ -734,39 +1050,39 @@
           <t>Timepoint</t>
         </is>
       </c>
-      <c r="AH2" s="2" t="n"/>
+      <c r="AH2" s="12" t="n"/>
       <c r="AI2" s="2" t="inlineStr">
         <is>
           <t>Weight Loss</t>
         </is>
       </c>
-      <c r="AJ2" s="2" t="n"/>
-      <c r="AK2" s="2" t="n"/>
-      <c r="AL2" s="2" t="n"/>
+      <c r="AJ2" s="11" t="n"/>
+      <c r="AK2" s="11" t="n"/>
+      <c r="AL2" s="12" t="n"/>
       <c r="AM2" s="2" t="inlineStr">
         <is>
           <t>Waist Circumference Reduction</t>
         </is>
       </c>
-      <c r="AN2" s="2" t="n"/>
-      <c r="AO2" s="2" t="n"/>
-      <c r="AP2" s="2" t="n"/>
+      <c r="AN2" s="11" t="n"/>
+      <c r="AO2" s="11" t="n"/>
+      <c r="AP2" s="12" t="n"/>
       <c r="AQ2" s="2" t="inlineStr">
         <is>
           <t>Weight Loss &gt;= 5%</t>
         </is>
       </c>
-      <c r="AR2" s="2" t="n"/>
-      <c r="AS2" s="2" t="n"/>
-      <c r="AT2" s="2" t="n"/>
+      <c r="AR2" s="11" t="n"/>
+      <c r="AS2" s="11" t="n"/>
+      <c r="AT2" s="12" t="n"/>
       <c r="AU2" s="2" t="inlineStr">
         <is>
           <t>High Adherence</t>
         </is>
       </c>
-      <c r="AV2" s="2" t="n"/>
-      <c r="AW2" s="2" t="n"/>
-      <c r="AX2" s="2" t="n"/>
+      <c r="AV2" s="11" t="n"/>
+      <c r="AW2" s="11" t="n"/>
+      <c r="AX2" s="12" t="n"/>
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr"/>
@@ -2827,8 +3143,8 @@
   </sheetData>
   <mergeCells count="14">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="AU2:AX2"/>
     <mergeCell ref="AI1:AX1"/>
-    <mergeCell ref="AU2:AX2"/>
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="U2:Y2"/>
     <mergeCell ref="Z2:AD2"/>
@@ -2842,6 +3158,7 @@
     <mergeCell ref="AE1:AH1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2988,6 +3305,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3176,6 +3494,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3508,6 +3827,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5134,6 +5454,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6160,6 +6481,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6226,6 +6548,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7572,6 +7895,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8094,5 +8418,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>